--- a/public/downloads/HubertAcidic2020.xlsx
+++ b/public/downloads/HubertAcidic2020.xlsx
@@ -8,29 +8,31 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-m-1p1_omat" sheetId="15" r:id="rId15"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="16" r:id="rId16"/>
-    <sheet name="UMA-s-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-m-1p1_omat" sheetId="17" r:id="rId17"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="18" r:id="rId18"/>
+    <sheet name="UMA-s-1p1_omat" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="55">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -62,10 +64,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -167,13 +169,34 @@
     <t>Adsorbate_name</t>
   </si>
   <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
+  </si>
+  <si>
     <t>O</t>
   </si>
   <si>
-    <t>OOH</t>
+    <t>OH</t>
   </si>
   <si>
-    <t>OH</t>
+    <t>OOH</t>
   </si>
 </sst>
 </file>
@@ -659,10 +682,10 @@
         <v>39</v>
       </c>
       <c r="N3" s="5">
-        <v>173.5812528133392</v>
+        <v>173581.2528133392</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03176816486334905</v>
+        <v>31.76816486334905</v>
       </c>
       <c r="P3" s="5">
         <v>5464</v>
@@ -709,10 +732,10 @@
         <v>39</v>
       </c>
       <c r="N4" s="5">
-        <v>299.954735994339</v>
+        <v>299954.735994339</v>
       </c>
       <c r="O4" s="4">
-        <v>0.05141493589207045</v>
+        <v>51.41493589207045</v>
       </c>
       <c r="P4" s="5">
         <v>5834</v>
@@ -759,10 +782,10 @@
         <v>39</v>
       </c>
       <c r="N5" s="5">
-        <v>765.0304720401764</v>
+        <v>765030.4720401764</v>
       </c>
       <c r="O5" s="4">
-        <v>0.1406047550156546</v>
+        <v>140.6047550156545</v>
       </c>
       <c r="P5" s="5">
         <v>5441</v>
@@ -809,10 +832,10 @@
         <v>39</v>
       </c>
       <c r="N6" s="5">
-        <v>626.3920786380768</v>
+        <v>626392.0786380768</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08556099967737697</v>
+        <v>85.56099967737697</v>
       </c>
       <c r="P6" s="5">
         <v>7321</v>
@@ -859,10 +882,10 @@
         <v>39</v>
       </c>
       <c r="N7" s="5">
-        <v>920.7792158126831</v>
+        <v>920779.2158126831</v>
       </c>
       <c r="O7" s="4">
-        <v>0.19392991065979</v>
+        <v>193.92991065979</v>
       </c>
       <c r="P7" s="5">
         <v>4748</v>
@@ -909,10 +932,10 @@
         <v>39</v>
       </c>
       <c r="N8" s="5">
-        <v>96.48134064674377</v>
+        <v>96481.34064674377</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01441956966772437</v>
+        <v>14.41956966772437</v>
       </c>
       <c r="P8" s="5">
         <v>6691</v>
@@ -959,10 +982,10 @@
         <v>39</v>
       </c>
       <c r="N9" s="5">
-        <v>480.9644708633423</v>
+        <v>480964.4708633423</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02978292593122437</v>
+        <v>29.78292593122437</v>
       </c>
       <c r="P9" s="5">
         <v>16149</v>
@@ -1009,10 +1032,10 @@
         <v>39</v>
       </c>
       <c r="N10" s="5">
-        <v>411.4356825351715</v>
+        <v>411435.6825351715</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08168268464069317</v>
+        <v>81.68268464069317</v>
       </c>
       <c r="P10" s="5">
         <v>5037</v>
@@ -1059,10 +1082,10 @@
         <v>39</v>
       </c>
       <c r="N11" s="5">
-        <v>242.8128087520599</v>
+        <v>242812.8087520599</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03947533876638919</v>
+        <v>39.47533876638919</v>
       </c>
       <c r="P11" s="5">
         <v>6151</v>
@@ -1109,10 +1132,10 @@
         <v>39</v>
       </c>
       <c r="N12" s="5">
-        <v>86.20244455337524</v>
+        <v>86202.44455337524</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01923732304248499</v>
+        <v>19.23732304248499</v>
       </c>
       <c r="P12" s="5">
         <v>4481</v>
@@ -1159,10 +1182,10 @@
         <v>39</v>
       </c>
       <c r="N13" s="5">
-        <v>457.6944661140442</v>
+        <v>457694.4661140442</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07280013776269194</v>
+        <v>72.80013776269193</v>
       </c>
       <c r="P13" s="5">
         <v>6287</v>
@@ -1209,10 +1232,10 @@
         <v>39</v>
       </c>
       <c r="N14" s="5">
-        <v>1368.035485982895</v>
+        <v>1368035.485982895</v>
       </c>
       <c r="O14" s="4">
-        <v>0.260826594086348</v>
+        <v>260.8265940863479</v>
       </c>
       <c r="P14" s="5">
         <v>5245</v>
@@ -1259,10 +1282,10 @@
         <v>39</v>
       </c>
       <c r="N15" s="5">
-        <v>840.3135802745819</v>
+        <v>840313.5802745819</v>
       </c>
       <c r="O15" s="4">
-        <v>0.2551043048799581</v>
+        <v>255.1043048799581</v>
       </c>
       <c r="P15" s="5">
         <v>3294</v>
@@ -1309,10 +1332,10 @@
         <v>39</v>
       </c>
       <c r="N16" s="5">
-        <v>1099.692397594452</v>
+        <v>1099692.397594452</v>
       </c>
       <c r="O16" s="4">
-        <v>0.09887541787398417</v>
+        <v>98.87541787398418</v>
       </c>
       <c r="P16" s="5">
         <v>11122</v>
@@ -1359,10 +1382,10 @@
         <v>39</v>
       </c>
       <c r="N17" s="5">
-        <v>369.5711579322815</v>
+        <v>369571.1579322815</v>
       </c>
       <c r="O17" s="4">
-        <v>0.09950758156496541</v>
+        <v>99.50758156496541</v>
       </c>
       <c r="P17" s="5">
         <v>3714</v>
@@ -1390,7 +1413,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1401,9 +1424,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1437,8 +1466,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1460,25 +1497,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1428871317827972</v>
+        <v>0.3074559906375984</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1518467783625274</v>
+        <v>0.2841410760068002</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1786633600201165</v>
+        <v>0.353969765655257</v>
       </c>
       <c r="E3" s="4">
-        <v>87.48822605965462</v>
+        <v>87.67660910518046</v>
       </c>
       <c r="F3" s="4">
-        <v>91.46360351058335</v>
+        <v>87.34124935467199</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -1501,91 +1556,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2841410760068002</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2138468697903969</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.2064096180895653</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.08693132807274696</v>
+        <v>0.2842723529294363</v>
       </c>
       <c r="C4" s="4">
-        <v>0.08693132807274696</v>
+        <v>0.2552487662515539</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1034988172605066</v>
+        <v>0.299844286816765</v>
       </c>
       <c r="E4" s="4">
-        <v>88.19466248037666</v>
+        <v>86.7032967032968</v>
       </c>
       <c r="F4" s="4">
-        <v>91.70108415074871</v>
+        <v>88.51574599896738</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2552487662515539</v>
+      </c>
+      <c r="O4" s="5">
+        <v>11</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1641242227757778</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1596643881156946</v>
+      </c>
+      <c r="R4" s="5">
+        <v>11</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.106456412820838</v>
+        <v>0.4759449615196303</v>
       </c>
       <c r="C5" s="4">
-        <v>0.106456412820838</v>
+        <v>0.5810191626221045</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1363841973946096</v>
+        <v>0.6367079004214459</v>
       </c>
       <c r="E5" s="4">
-        <v>87.59811616954467</v>
+        <v>78.39874411302934</v>
       </c>
       <c r="F5" s="4">
-        <v>91.37325761486849</v>
+        <v>70.21424883841073</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.5810191626221045</v>
+      </c>
+      <c r="O5" s="5">
+        <v>7</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.3266099098417594</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09402700856120083</v>
+      </c>
+      <c r="R5" s="5">
+        <v>7</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1596,6 +1705,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1603,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1614,9 +1724,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1650,8 +1766,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1673,132 +1797,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1437598887469825</v>
+        <v>0.8299720885768544</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1307276552376161</v>
+        <v>0.3846529860302823</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1535896537038884</v>
+        <v>0.8571881710223885</v>
       </c>
       <c r="E3" s="4">
-        <v>85.31397174254306</v>
+        <v>57.174254317112</v>
       </c>
       <c r="F3" s="4">
-        <v>87.96936843916711</v>
+        <v>58.91240750301196</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3846529860302823</v>
+      </c>
+      <c r="O3" s="5">
+        <v>8</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.6727390802666744</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.08106772427245446</v>
+      </c>
+      <c r="R3" s="5">
+        <v>8</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.3305979080094036</v>
+        <v>0.4051826729045925</v>
       </c>
       <c r="C4" s="4">
-        <v>0.3018488195308369</v>
+        <v>0.2268950187045359</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3403193155329255</v>
+        <v>0.5139742809814217</v>
       </c>
       <c r="E4" s="4">
-        <v>83.86970172684461</v>
+        <v>59.82731554160137</v>
       </c>
       <c r="F4" s="4">
-        <v>87.13302357597669</v>
+        <v>61.78540698674841</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.2268950187045359</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.3084721794938504</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1491070327893474</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1792865190995857</v>
+        <v>0.5983625864872868</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1371216199687439</v>
+        <v>0.4109933237658581</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1636743020034037</v>
+        <v>0.7604160980705326</v>
       </c>
       <c r="E5" s="4">
-        <v>83.18158032443741</v>
+        <v>56.85243328100524</v>
       </c>
       <c r="F5" s="4">
-        <v>81.24591292376486</v>
+        <v>58.06745826880162</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4109933237658581</v>
+      </c>
+      <c r="O5" s="5">
+        <v>8</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.334404263451023</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09056256693846443</v>
+      </c>
+      <c r="R5" s="5">
+        <v>8</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1809,6 +2005,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1816,7 +2013,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1827,9 +2024,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -1863,8 +2066,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1886,25 +2097,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1388328651544577</v>
+        <v>0.1428871317827972</v>
       </c>
       <c r="C3" s="4">
-        <v>0.116786612388907</v>
+        <v>0.1518467783625274</v>
       </c>
       <c r="D3" s="4">
-        <v>0.126815748831785</v>
+        <v>0.1786633600201165</v>
       </c>
       <c r="E3" s="4">
-        <v>90.42386185243311</v>
+        <v>87.48822605965462</v>
       </c>
       <c r="F3" s="4">
-        <v>91.99191189123979</v>
+        <v>91.46360351058335</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -1927,91 +2156,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.0991003958475587</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1145948400549929</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1188336581411153</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2241009124225876</v>
+        <v>0.106456412820838</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2008981040960786</v>
+        <v>0.106456412820838</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2085222756662775</v>
+        <v>0.1363841973946096</v>
       </c>
       <c r="E4" s="4">
-        <v>88.63683935112498</v>
+        <v>87.59811616954467</v>
       </c>
       <c r="F4" s="4">
-        <v>88.40905179831249</v>
+        <v>91.37325761486849</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.06547280116934751</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.08920638289229725</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08920638289229725</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1875460817813392</v>
+        <v>0.08693132807274696</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1526539236081987</v>
+        <v>0.08693132807274696</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1733087512712731</v>
+        <v>0.1034988172605066</v>
       </c>
       <c r="E5" s="4">
-        <v>89.14704343275758</v>
+        <v>88.19466248037666</v>
       </c>
       <c r="F5" s="4">
-        <v>90.08346239889811</v>
+        <v>91.70108415074871</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.03724708171536761</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06895591657590654</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06895591657590654</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2022,6 +2305,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2029,7 +2313,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2040,9 +2324,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2076,8 +2366,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2099,132 +2397,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.1832633069470175</v>
+        <v>0.1437598887469825</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1832633069470175</v>
+        <v>0.1307276552376161</v>
       </c>
       <c r="D3" s="4">
-        <v>0.19588337815354</v>
+        <v>0.1535896537038884</v>
       </c>
       <c r="E3" s="4">
-        <v>86.82103610675037</v>
+        <v>85.31397174254306</v>
       </c>
       <c r="F3" s="4">
-        <v>89.63603510583377</v>
+        <v>87.96936843916711</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.02705539469075783</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1403859095640449</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1293271273469969</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.1610451062006702</v>
+        <v>0.1792865190995857</v>
       </c>
       <c r="C4" s="4">
-        <v>0.1801613821164355</v>
+        <v>0.1371216199687439</v>
       </c>
       <c r="D4" s="4">
-        <v>0.1948291447329561</v>
+        <v>0.1636743020034037</v>
       </c>
       <c r="E4" s="4">
-        <v>81.04918890633151</v>
+        <v>83.18158032443741</v>
       </c>
       <c r="F4" s="4">
-        <v>83.82206160729622</v>
+        <v>81.24591292376486</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.07901389253342188</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.187153422090143</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1394472046031262</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1843935341109233</v>
+        <v>0.3305979080094036</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1640256827347571</v>
+        <v>0.3018488195308369</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1668622125221694</v>
+        <v>0.3403193155329255</v>
       </c>
       <c r="E5" s="4">
-        <v>84.16274201988476</v>
+        <v>83.86970172684461</v>
       </c>
       <c r="F5" s="4">
-        <v>83.97780072276596</v>
+        <v>87.13302357597669</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.3018488195308369</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1576714098888291</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.139665848194451</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2235,6 +2605,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2613,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2253,9 +2624,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2289,8 +2666,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2312,132 +2697,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3383647215941807</v>
+        <v>0.1388328651544577</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3383647215941807</v>
+        <v>0.116786612388907</v>
       </c>
       <c r="D3" s="4">
-        <v>0.3240158639162896</v>
+        <v>0.126815748831785</v>
       </c>
       <c r="E3" s="4">
-        <v>82.43328100470953</v>
+        <v>90.42386185243311</v>
       </c>
       <c r="F3" s="4">
-        <v>88.86422302529689</v>
+        <v>91.99191189123979</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.03136332020304641</v>
+      </c>
+      <c r="O3" s="5">
+        <v>12</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1460705544320837</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1272410524565891</v>
+      </c>
+      <c r="R3" s="5">
+        <v>12</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2753748556911857</v>
+        <v>0.1875460817813392</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2753748556911857</v>
+        <v>0.1526539236081987</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2560646483700572</v>
+        <v>0.1733087512712731</v>
       </c>
       <c r="E4" s="4">
-        <v>82.29984301412867</v>
+        <v>89.14704343275758</v>
       </c>
       <c r="F4" s="4">
-        <v>89.08879710893137</v>
+        <v>90.08346239889811</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.01423484345482014</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1842611179071499</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1479089757899254</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.212173053375108</v>
+        <v>0.2241009124225876</v>
       </c>
       <c r="C5" s="4">
-        <v>0.212173053375108</v>
+        <v>0.2008981040960786</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2064290351414386</v>
+        <v>0.2085222756662775</v>
       </c>
       <c r="E5" s="4">
-        <v>80.99424385138667</v>
+        <v>88.63683935112498</v>
       </c>
       <c r="F5" s="4">
-        <v>87.31371536740637</v>
+        <v>88.40905179831249</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.03754846793925518</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2154358813596826</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1883819481163269</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2448,6 +2905,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2455,7 +2913,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2466,9 +2924,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2502,8 +2966,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2525,25 +2997,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2271785884062033</v>
+        <v>0.1832633069470175</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2271785884062033</v>
+        <v>0.1832633069470175</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2477565762054591</v>
+        <v>0.19588337815354</v>
       </c>
       <c r="E3" s="4">
-        <v>95.83987441130287</v>
+        <v>86.82103610675037</v>
       </c>
       <c r="F3" s="4">
-        <v>96.09447599380491</v>
+        <v>89.63603510583377</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -2566,91 +3056,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1582036947861918</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1605708289330545</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1605708289330545</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.4541047872519931</v>
+        <v>0.1843935341109233</v>
       </c>
       <c r="C4" s="4">
-        <v>0.4541047872519931</v>
+        <v>0.1640256827347571</v>
       </c>
       <c r="D4" s="4">
-        <v>0.4804803375271968</v>
+        <v>0.1668622125221694</v>
       </c>
       <c r="E4" s="4">
-        <v>96.1381475667189</v>
+        <v>84.16274201988476</v>
       </c>
       <c r="F4" s="4">
-        <v>96.7268972638101</v>
+        <v>83.97780072276596</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="5">
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.1259552244225119</v>
+      </c>
+      <c r="O4" s="5">
+        <v>10</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.144598092171868</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1164150217249926</v>
+      </c>
+      <c r="R4" s="5">
+        <v>10</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2937280901527891</v>
+        <v>0.1610451062006702</v>
       </c>
       <c r="C5" s="4">
-        <v>0.2937280901527891</v>
+        <v>0.1801613821164355</v>
       </c>
       <c r="D5" s="4">
-        <v>0.3061781759623954</v>
+        <v>0.1948291447329561</v>
       </c>
       <c r="E5" s="4">
-        <v>94.52119309262153</v>
+        <v>81.04918890633151</v>
       </c>
       <c r="F5" s="4">
-        <v>95.4904491481672</v>
+        <v>83.82206160729622</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.07727036190613035</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1260117646334213</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1450384903409217</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2661,6 +3205,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2668,7 +3213,7 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2679,9 +3224,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2715,8 +3266,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2738,132 +3297,204 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.6421466766322295</v>
+        <v>0.3383647215941807</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4480221231103311</v>
+        <v>0.3383647215941807</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4978984033719925</v>
+        <v>0.3240158639162896</v>
       </c>
       <c r="E3" s="4">
-        <v>64.74882260596502</v>
+        <v>82.43328100470953</v>
       </c>
       <c r="F3" s="4">
-        <v>70.07571846498138</v>
+        <v>88.86422302529689</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
       </c>
       <c r="H3" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.3383647215941807</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09694863112086546</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09694863112086546</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.7590001381529293</v>
+        <v>0.212173053375108</v>
       </c>
       <c r="C4" s="4">
-        <v>0.5195863095416726</v>
+        <v>0.212173053375108</v>
       </c>
       <c r="D4" s="4">
-        <v>0.5441426630372178</v>
+        <v>0.2064290351414386</v>
       </c>
       <c r="E4" s="4">
-        <v>62.73940345368902</v>
+        <v>80.99424385138667</v>
       </c>
       <c r="F4" s="4">
-        <v>67.31629667871249</v>
+        <v>87.31371536740637</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
       </c>
       <c r="J4" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.212173053375108</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.04120002294756089</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04120002294756089</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.7858533289853334</v>
+        <v>0.2753748556911857</v>
       </c>
       <c r="C5" s="4">
-        <v>0.4585154380045842</v>
+        <v>0.2753748556911857</v>
       </c>
       <c r="D5" s="4">
-        <v>0.479787068395094</v>
+        <v>0.2560646483700572</v>
       </c>
       <c r="E5" s="4">
-        <v>59.46363160648883</v>
+        <v>82.29984301412867</v>
       </c>
       <c r="F5" s="4">
-        <v>64.4458785062819</v>
+        <v>89.08879710893137</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" s="5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2753748556911857</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.05853481711082912</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.05853481711082912</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2874,6 +3505,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2881,7 +3513,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2892,9 +3524,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -2928,8 +3566,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2951,25 +3597,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2041711382107484</v>
+        <v>0.2271785884062033</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2041711382107484</v>
+        <v>0.2271785884062033</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2175991476841002</v>
+        <v>0.2477565762054591</v>
       </c>
       <c r="E3" s="4">
-        <v>94.81161695447408</v>
+        <v>95.83987441130287</v>
       </c>
       <c r="F3" s="4">
-        <v>95.83892617449661</v>
+        <v>96.09447599380491</v>
       </c>
       <c r="G3" s="5">
         <v>13</v>
@@ -2992,34 +3656,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>-0.2271785884062033</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0457271870504475</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0457271870504475</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.219517551398944</v>
+        <v>0.2937280901527891</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2184468629737181</v>
+        <v>0.2937280901527891</v>
       </c>
       <c r="D4" s="4">
-        <v>0.2223716241027484</v>
+        <v>0.3061781759623954</v>
       </c>
       <c r="E4" s="4">
-        <v>93.12401883830479</v>
+        <v>94.52119309262153</v>
       </c>
       <c r="F4" s="4">
-        <v>92.39545689209972</v>
+        <v>95.4904491481672</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I4" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5">
         <v>0</v>
@@ -3033,34 +3715,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>-0.2937280901527891</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06020185808886454</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06020185808886454</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.2086131118989477</v>
+        <v>0.4541047872519931</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1828719131732498</v>
+        <v>0.4541047872519931</v>
       </c>
       <c r="D5" s="4">
-        <v>0.1942625589273968</v>
+        <v>0.4804803375271968</v>
       </c>
       <c r="E5" s="4">
-        <v>93.60020931449499</v>
+        <v>96.1381475667189</v>
       </c>
       <c r="F5" s="4">
-        <v>92.18120805369003</v>
+        <v>96.7268972638101</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -3074,9 +3774,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>-0.4541047872519931</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.06086316700552007</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.06086316700552007</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3087,12 +3805,1470 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.6421466766322295</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.4480221231103311</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.4978984033719925</v>
+      </c>
+      <c r="E3" s="4">
+        <v>64.74882260596502</v>
+      </c>
+      <c r="F3" s="4">
+        <v>70.07571846498138</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>9</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>4</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>4</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0.4480221231103311</v>
+      </c>
+      <c r="O3" s="5">
+        <v>9</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.3172069721846377</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07822524404388347</v>
+      </c>
+      <c r="R3" s="5">
+        <v>9</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.7858533289853334</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.4585154380045842</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.479787068395094</v>
+      </c>
+      <c r="E4" s="4">
+        <v>59.46363160648883</v>
+      </c>
+      <c r="F4" s="4">
+        <v>64.4458785062819</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>9</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>4</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>4</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.4585154380045842</v>
+      </c>
+      <c r="O4" s="5">
+        <v>9</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.4980407677106606</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.04278618283005669</v>
+      </c>
+      <c r="R4" s="5">
+        <v>9</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.7590001381529293</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.5195863095416726</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.5441426630372178</v>
+      </c>
+      <c r="E5" s="4">
+        <v>62.73940345368902</v>
+      </c>
+      <c r="F5" s="4">
+        <v>67.31629667871249</v>
+      </c>
+      <c r="G5" s="5">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5">
+        <v>9</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>4</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>0.5195863095416726</v>
+      </c>
+      <c r="O5" s="5">
+        <v>9</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.2734623282124252</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.04918116609057677</v>
+      </c>
+      <c r="R5" s="5">
+        <v>9</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.2041711382107484</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.2041711382107484</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.2175991476841002</v>
+      </c>
+      <c r="E3" s="4">
+        <v>94.81161695447408</v>
+      </c>
+      <c r="F3" s="4">
+        <v>95.83892617449661</v>
+      </c>
+      <c r="G3" s="5">
+        <v>13</v>
+      </c>
+      <c r="H3" s="5">
+        <v>13</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.2041711382107484</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.06564330956672569</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06564330956672569</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="4">
+        <v>0.2086131118989477</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1828719131732498</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1942625589273968</v>
+      </c>
+      <c r="E4" s="4">
+        <v>93.60020931449499</v>
+      </c>
+      <c r="F4" s="4">
+        <v>92.18120805369003</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>-0.1828719131732498</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09976196138479446</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.08018915954735462</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
+        <v>0.219517551398944</v>
+      </c>
+      <c r="C5" s="4">
+        <v>0.2184468629737181</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0.2223716241027484</v>
+      </c>
+      <c r="E5" s="4">
+        <v>93.12401883830479</v>
+      </c>
+      <c r="F5" s="4">
+        <v>92.39545689209972</v>
+      </c>
+      <c r="G5" s="5">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5">
+        <v>12</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4">
+        <v>-0.2178745687949313</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.1143448592261962</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1226659938528189</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>97.43589743589743</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1281031997854639</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.1295221022865</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.1568394511201326</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.85382871097174</v>
+      </c>
+      <c r="L3" s="4">
+        <v>88.13514598749505</v>
+      </c>
+      <c r="M3" s="5">
+        <v>39</v>
+      </c>
+      <c r="N3" s="5">
+        <v>173581.2528133392</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.76816486334905</v>
+      </c>
+      <c r="P3" s="5">
+        <v>5464</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>100</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1040909104757614</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.1040909104757614</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.184793281014352</v>
+      </c>
+      <c r="K4" s="4">
+        <v>83.67695796267225</v>
+      </c>
+      <c r="L4" s="4">
+        <v>87.82510181839042</v>
+      </c>
+      <c r="M4" s="5">
+        <v>39</v>
+      </c>
+      <c r="N4" s="5">
+        <v>299954.735994339</v>
+      </c>
+      <c r="O4" s="4">
+        <v>51.41493589207045</v>
+      </c>
+      <c r="P4" s="5">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.08623896169522165</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.08503854888648345</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.1128496285675564</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.43467643467652</v>
+      </c>
+      <c r="L5" s="4">
+        <v>89.22933516893235</v>
+      </c>
+      <c r="M5" s="5">
+        <v>39</v>
+      </c>
+      <c r="N5" s="5">
+        <v>765030.4720401764</v>
+      </c>
+      <c r="O5" s="4">
+        <v>140.6047550156545</v>
+      </c>
+      <c r="P5" s="5">
+        <v>5441</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>71.7948717948718</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="D6" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.1382730864226216</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.08808425465178117</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.1953070774963913</v>
+      </c>
+      <c r="K6" s="4">
+        <v>76.93615907901597</v>
+      </c>
+      <c r="L6" s="4">
+        <v>76.98015258417848</v>
+      </c>
+      <c r="M6" s="5">
+        <v>39</v>
+      </c>
+      <c r="N6" s="5">
+        <v>626392.0786380768</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.56099967737697</v>
+      </c>
+      <c r="P6" s="5">
+        <v>7321</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>97.43589743589743</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.08599551651040786</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.07926236149404446</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.07360441025201638</v>
+      </c>
+      <c r="K7" s="4">
+        <v>90.38548752834464</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.00384328572319</v>
+      </c>
+      <c r="M7" s="5">
+        <v>39</v>
+      </c>
+      <c r="N7" s="5">
+        <v>920779.2158126831</v>
+      </c>
+      <c r="O7" s="4">
+        <v>193.92991065979</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>76.92307692307693</v>
+      </c>
+      <c r="C8" s="3">
+        <v>12.82051282051282</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.234860334135978</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.1630470915425276</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.2042146514296665</v>
+      </c>
+      <c r="K8" s="4">
+        <v>84.25954997383553</v>
+      </c>
+      <c r="L8" s="4">
+        <v>82.02374806401504</v>
+      </c>
+      <c r="M8" s="5">
+        <v>39</v>
+      </c>
+      <c r="N8" s="5">
+        <v>96481.34064674377</v>
+      </c>
+      <c r="O8" s="4">
+        <v>14.41956966772437</v>
+      </c>
+      <c r="P8" s="5">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>64.1025641025641</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>35.8974358974359</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>35.8974358974359</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.4385385077371826</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1086002249916591</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.4134500546662846</v>
+      </c>
+      <c r="K9" s="4">
+        <v>57.95133437990611</v>
+      </c>
+      <c r="L9" s="4">
+        <v>59.58842425285314</v>
+      </c>
+      <c r="M9" s="5">
+        <v>39</v>
+      </c>
+      <c r="N9" s="5">
+        <v>480964.4708633423</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.78292593122437</v>
+      </c>
+      <c r="P9" s="5">
+        <v>16149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>97.43589743589743</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.09091904650773222</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.09163457344157981</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.1244874417201523</v>
+      </c>
+      <c r="K10" s="4">
+        <v>87.76033490319197</v>
+      </c>
+      <c r="L10" s="4">
+        <v>91.51264842540003</v>
+      </c>
+      <c r="M10" s="5">
+        <v>39</v>
+      </c>
+      <c r="N10" s="5">
+        <v>411435.6825351715</v>
+      </c>
+      <c r="O10" s="4">
+        <v>81.68268464069317</v>
+      </c>
+      <c r="P10" s="5">
+        <v>5037</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>87.17948717948718</v>
+      </c>
+      <c r="C11" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1617369138476723</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1359525809567246</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1594332780295425</v>
+      </c>
+      <c r="K11" s="4">
+        <v>84.12175126460838</v>
+      </c>
+      <c r="L11" s="4">
+        <v>85.44943497963479</v>
+      </c>
+      <c r="M11" s="5">
+        <v>39</v>
+      </c>
+      <c r="N11" s="5">
+        <v>242812.8087520599</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.47533876638919</v>
+      </c>
+      <c r="P11" s="5">
+        <v>6151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>92.30769230769231</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>7.692307692307693</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.1819225178996388</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.1545106587876138</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.1671786151552478</v>
+      </c>
+      <c r="K12" s="4">
+        <v>89.40258154543861</v>
+      </c>
+      <c r="L12" s="4">
+        <v>90.16147536281706</v>
+      </c>
+      <c r="M12" s="5">
+        <v>39</v>
+      </c>
+      <c r="N12" s="5">
+        <v>86202.44455337524</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.23732304248499</v>
+      </c>
+      <c r="P12" s="5">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>87.17948717948718</v>
+      </c>
+      <c r="C13" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="D13" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10.25641025641026</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.1437268952461146</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.1425586584449933</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.1592011322510214</v>
+      </c>
+      <c r="K13" s="4">
+        <v>84.01098901098891</v>
+      </c>
+      <c r="L13" s="4">
+        <v>85.81196581196683</v>
+      </c>
+      <c r="M13" s="5">
+        <v>39</v>
+      </c>
+      <c r="N13" s="5">
+        <v>457694.4661140442</v>
+      </c>
+      <c r="O13" s="4">
+        <v>72.80013776269193</v>
+      </c>
+      <c r="P13" s="5">
+        <v>6287</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.06556115705975184</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.06556115705975184</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.05126534200207447</v>
+      </c>
+      <c r="K14" s="4">
+        <v>81.90912262340832</v>
+      </c>
+      <c r="L14" s="4">
+        <v>88.4222451672112</v>
+      </c>
+      <c r="M14" s="5">
+        <v>39</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1368035.485982895</v>
+      </c>
+      <c r="O14" s="4">
+        <v>260.8265940863479</v>
+      </c>
+      <c r="P14" s="5">
+        <v>5245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.05559740404827736</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.05559740404827736</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.04719270808241108</v>
+      </c>
+      <c r="K15" s="4">
+        <v>95.49973835688124</v>
+      </c>
+      <c r="L15" s="4">
+        <v>96.10394080192728</v>
+      </c>
+      <c r="M15" s="5">
+        <v>39</v>
+      </c>
+      <c r="N15" s="5">
+        <v>840313.5802745819</v>
+      </c>
+      <c r="O15" s="4">
+        <v>255.1043048799581</v>
+      </c>
+      <c r="P15" s="5">
+        <v>3294</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3">
+        <v>69.23076923076923</v>
+      </c>
+      <c r="C16" s="3">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3">
+        <v>30.76923076923077</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2.564102564102564</v>
+      </c>
+      <c r="F16" s="3">
+        <v>28.2051282051282</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0.3629033560359078</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0.05673086432150564</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.1057921688339227</v>
+      </c>
+      <c r="K16" s="4">
+        <v>62.31728588871481</v>
+      </c>
+      <c r="L16" s="4">
+        <v>67.27929788332388</v>
+      </c>
+      <c r="M16" s="5">
+        <v>39</v>
+      </c>
+      <c r="N16" s="5">
+        <v>1099692.397594452</v>
+      </c>
+      <c r="O16" s="4">
+        <v>98.87541787398418</v>
+      </c>
+      <c r="P16" s="5">
+        <v>11122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>94.87179487179486</v>
+      </c>
+      <c r="C17" s="3">
+        <v>5.128205128205128</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.09325004339257212</v>
+      </c>
+      <c r="I17" s="4">
+        <v>0.0888547260856626</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.08932307863232167</v>
+      </c>
+      <c r="K17" s="4">
+        <v>93.84528170242461</v>
+      </c>
+      <c r="L17" s="4">
+        <v>93.47186370676059</v>
+      </c>
+      <c r="M17" s="5">
+        <v>39</v>
+      </c>
+      <c r="N17" s="5">
+        <v>369571.1579322815</v>
+      </c>
+      <c r="O17" s="4">
+        <v>99.50758156496541</v>
+      </c>
+      <c r="P17" s="5">
+        <v>3714</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3787,7 +5963,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="5">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="25" customHeight="1">
@@ -3847,9 +6023,764 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>39</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>36</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>3</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>28</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>38</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>30</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>25</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>14</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>14</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>14</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>38</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>34</v>
+      </c>
+      <c r="C11" s="5">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>36</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>0</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>4</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>39</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>39</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="25" customHeight="1">
+      <c r="A16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5">
+        <v>27</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>12</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <v>5</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0</v>
+      </c>
+      <c r="N16" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25" customHeight="1">
+      <c r="A17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="5">
+        <v>37</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3860,9 +6791,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -3896,8 +6833,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3919,10 +6864,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2736053295893769</v>
@@ -3960,91 +6923,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.2736053295893769</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1061071413063905</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1061071413063905</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
+        <v>0.1348440305025961</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1348440305025961</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1667992909994692</v>
+      </c>
+      <c r="E4" s="4">
+        <v>85.578231292517</v>
+      </c>
+      <c r="F4" s="4">
+        <v>88.35656513508863</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>13</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.07117880260077833</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1451105569397182</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.1451105569397182</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.4176550033169738</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.4233615344512884</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.4237659832774888</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>85.01831501831523</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>86.67613147478818</v>
       </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G5" s="5">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5">
         <v>12</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>1</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1348440305025961</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1348440305025961</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1667992909994692</v>
-      </c>
-      <c r="E5" s="4">
-        <v>85.578231292517</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.35656513508863</v>
-      </c>
-      <c r="G5" s="5">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5">
-        <v>13</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>0</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.4233615344512884</v>
+      </c>
+      <c r="O5" s="5">
+        <v>12</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.133091901110283</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.1380008174739658</v>
+      </c>
+      <c r="R5" s="5">
+        <v>12</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4055,14 +7072,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4073,9 +7091,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4109,8 +7133,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4132,10 +7164,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.06083390871882207</v>
@@ -4173,78 +7223,112 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.005274572154825399</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.0588052271208123</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.0588052271208123</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
+        <v>0.06736241074105684</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.06736241074105684</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1298636962360849</v>
+      </c>
+      <c r="E4" s="4">
+        <v>83.33594976452115</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.65444845981769</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>13</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.01374862696624746</v>
+      </c>
+      <c r="O4" s="5">
+        <v>13</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.06412052342709383</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06412052342709383</v>
+      </c>
+      <c r="R4" s="5">
+        <v>13</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>3.763579802575866</v>
       </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="C5" s="4"/>
+      <c r="D5" s="4">
         <v>3.858119151471599</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>83.85661957090524</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>87.60884529340908</v>
       </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>13</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.06736241074105684</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06736241074105684</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1298636962360849</v>
-      </c>
-      <c r="E5" s="4">
-        <v>83.33594976452115</v>
-      </c>
-      <c r="F5" s="4">
-        <v>87.65444845981769</v>
-      </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -4253,11 +7337,29 @@
         <v>0</v>
       </c>
       <c r="M5" s="5">
+        <v>13</v>
+      </c>
+      <c r="N5" s="4">
+        <v>3.763579802575866</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.189346980879378</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.189346980879378</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4268,14 +7370,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4286,9 +7389,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4322,8 +7431,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4345,10 +7462,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.09870049666154028</v>
@@ -4386,91 +7521,145 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.05910295602238263</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09399194032746047</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09399194032746047</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
+        <v>0.07272921291078223</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.06297984904131226</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1078274499683381</v>
+      </c>
+      <c r="E4" s="4">
+        <v>86.96232339089482</v>
+      </c>
+      <c r="F4" s="4">
+        <v>90.38203407330903</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.01262863094403125</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.07370064606032309</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.06508462086531747</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.09450671295654117</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.1086451578093643</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.1270433019257273</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>83.69178440606994</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>85.48098434004449</v>
       </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="G5" s="5">
+        <v>13</v>
+      </c>
+      <c r="H5" s="5">
         <v>11</v>
       </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
         <v>2</v>
       </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
         <v>2</v>
       </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.07272921291078223</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.06297984904131226</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1078274499683381</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.96232339089482</v>
-      </c>
-      <c r="F5" s="4">
-        <v>90.38203407330903</v>
-      </c>
-      <c r="G5" s="5">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5">
-        <v>12</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.0456741326339108</v>
+      </c>
+      <c r="O5" s="5">
+        <v>11</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09102429869788138</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09622518957023715</v>
+      </c>
+      <c r="R5" s="5">
+        <v>11</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4481,14 +7670,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4499,9 +7689,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4535,8 +7731,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4558,10 +7762,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.2307040160805076</v>
@@ -4599,34 +7821,52 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.170237371803961</v>
+      </c>
+      <c r="O3" s="5">
+        <v>10</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1328572662944571</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09500752974217334</v>
+      </c>
+      <c r="R3" s="5">
+        <v>10</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
-        <v>0.2635436913310776</v>
+        <v>0.1764606534056991</v>
       </c>
       <c r="C4" s="4">
-        <v>0.2107319703953806</v>
+        <v>0.1015642976087747</v>
       </c>
       <c r="D4" s="4">
-        <v>0.3136290525183523</v>
+        <v>0.2338902315893913</v>
       </c>
       <c r="E4" s="4">
-        <v>76.19832548403973</v>
+        <v>75.01046572475114</v>
       </c>
       <c r="F4" s="4">
-        <v>75.67458268800549</v>
+        <v>71.94544828773141</v>
       </c>
       <c r="G4" s="5">
         <v>13</v>
       </c>
       <c r="H4" s="5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="5">
         <v>3</v>
@@ -4640,34 +7880,52 @@
       <c r="M4" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
+      <c r="N4" s="4">
+        <v>0.0188044097417901</v>
+      </c>
+      <c r="O4" s="5">
+        <v>8</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.1735097857083758</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.0991196888183481</v>
+      </c>
+      <c r="R4" s="5">
+        <v>8</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4">
-        <v>0.1764606534056991</v>
+        <v>0.2635436913310776</v>
       </c>
       <c r="C5" s="4">
-        <v>0.1015642976087747</v>
+        <v>0.2107319703953806</v>
       </c>
       <c r="D5" s="4">
-        <v>0.2338902315893913</v>
+        <v>0.3136290525183523</v>
       </c>
       <c r="E5" s="4">
-        <v>75.01046572475114</v>
+        <v>76.19832548403973</v>
       </c>
       <c r="F5" s="4">
-        <v>71.94544828773141</v>
+        <v>75.67458268800549</v>
       </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I5" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>3</v>
@@ -4681,9 +7939,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.2107319703953806</v>
+      </c>
+      <c r="O5" s="5">
+        <v>10</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.108452207265032</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.07233263222813549</v>
+      </c>
+      <c r="R5" s="5">
+        <v>10</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4694,14 +7970,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -4712,9 +7989,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>44</v>
       </c>
@@ -4748,8 +8031,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4771,10 +8062,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4">
         <v>0.1433644857431292</v>
@@ -4812,75 +8121,111 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
+      <c r="N3" s="4">
+        <v>0.1433644857431292</v>
+      </c>
+      <c r="O3" s="5">
+        <v>13</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.07196181708070594</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.07196181708070594</v>
+      </c>
+      <c r="R3" s="5">
+        <v>13</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="25" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B4" s="4">
+        <v>0.1301942926210109</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0.1227882179037205</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0.1078788638138257</v>
+      </c>
+      <c r="E4" s="4">
+        <v>89.869178440607</v>
+      </c>
+      <c r="F4" s="4">
+        <v>87.72500430218555</v>
+      </c>
+      <c r="G4" s="5">
+        <v>13</v>
+      </c>
+      <c r="H4" s="5">
+        <v>12</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0.1227882179037205</v>
+      </c>
+      <c r="O4" s="5">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0.09350277899317587</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0.07280672664825576</v>
+      </c>
+      <c r="R4" s="5">
+        <v>12</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.1661359468500642</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C5" s="4">
         <v>0.1661359468500642</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D5" s="4">
         <v>0.147251269696697</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>90.83725798011506</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F5" s="4">
         <v>92.9633453794528</v>
       </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>13</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>0</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.1301942926210109</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.1227882179037205</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.1078788638138257</v>
-      </c>
-      <c r="E5" s="4">
-        <v>89.869178440607</v>
-      </c>
-      <c r="F5" s="4">
-        <v>87.72500430218555</v>
-      </c>
       <c r="G5" s="5">
         <v>13</v>
       </c>
       <c r="H5" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5">
         <v>0</v>
@@ -4894,9 +8239,27 @@
       <c r="M5" s="5">
         <v>0</v>
       </c>
+      <c r="N5" s="4">
+        <v>0.1661359468500642</v>
+      </c>
+      <c r="O5" s="5">
+        <v>13</v>
+      </c>
+      <c r="P5" s="4">
+        <v>0.09252195345734181</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.09252195345734181</v>
+      </c>
+      <c r="R5" s="5">
+        <v>13</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -4907,432 +8270,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3074559906375984</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.2841410760068002</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.353969765655257</v>
-      </c>
-      <c r="E3" s="4">
-        <v>87.67660910518046</v>
-      </c>
-      <c r="F3" s="4">
-        <v>87.34124935467199</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>12</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.4759449615196303</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.5810191626221045</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.6367079004214459</v>
-      </c>
-      <c r="E4" s="4">
-        <v>78.39874411302934</v>
-      </c>
-      <c r="F4" s="4">
-        <v>70.21424883841073</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>7</v>
-      </c>
-      <c r="I4" s="5">
-        <v>5</v>
-      </c>
-      <c r="J4" s="5">
-        <v>1</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>1</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.2842723529294363</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2552487662515539</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.299844286816765</v>
-      </c>
-      <c r="E5" s="4">
-        <v>86.7032967032968</v>
-      </c>
-      <c r="F5" s="4">
-        <v>88.51574599896738</v>
-      </c>
-      <c r="G5" s="5">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5">
-        <v>11</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>2</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>2</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.8299720885768544</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3846529860302823</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.8571881710223885</v>
-      </c>
-      <c r="E3" s="4">
-        <v>57.174254317112</v>
-      </c>
-      <c r="F3" s="4">
-        <v>58.91240750301196</v>
-      </c>
-      <c r="G3" s="5">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5">
-        <v>8</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>5</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>5</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="25" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.5983625864872868</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0.4109933237658581</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0.7604160980705326</v>
-      </c>
-      <c r="E4" s="4">
-        <v>56.85243328100524</v>
-      </c>
-      <c r="F4" s="4">
-        <v>58.06745826880162</v>
-      </c>
-      <c r="G4" s="5">
-        <v>13</v>
-      </c>
-      <c r="H4" s="5">
-        <v>8</v>
-      </c>
-      <c r="I4" s="5">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5">
-        <v>5</v>
-      </c>
-      <c r="K4" s="5">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
-        <v>5</v>
-      </c>
-      <c r="M4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="25" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4">
-        <v>0.4051826729045925</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.2268950187045359</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0.5139742809814217</v>
-      </c>
-      <c r="E5" s="4">
-        <v>59.82731554160137</v>
-      </c>
-      <c r="F5" s="4">
-        <v>61.78540698674841</v>
-      </c>
-      <c r="G5" s="5">
-        <v>13</v>
-      </c>
-      <c r="H5" s="5">
-        <v>9</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="5">
-        <v>4</v>
-      </c>
-      <c r="K5" s="5">
-        <v>0</v>
-      </c>
-      <c r="L5" s="5">
-        <v>4</v>
-      </c>
-      <c r="M5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/HubertAcidic2020.xlsx
+++ b/public/downloads/HubertAcidic2020.xlsx
@@ -1557,16 +1557,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2841410760068002</v>
+        <v>0.2423334846973226</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2138468697903969</v>
+        <v>0.2072993748394299</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.2064096180895653</v>
+        <v>0.1958325326168945</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -1616,16 +1616,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2552487662515539</v>
+        <v>0.1593553868138358</v>
       </c>
       <c r="O4" s="5">
         <v>11</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1641242227757778</v>
+        <v>0.1556511450497245</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1596643881156946</v>
+        <v>0.1322155909053193</v>
       </c>
       <c r="R4" s="5">
         <v>11</v>
@@ -1675,16 +1675,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5810191626221045</v>
+        <v>0.5473898132314048</v>
       </c>
       <c r="O5" s="5">
         <v>7</v>
       </c>
       <c r="P5" s="4">
-        <v>0.3266099098417594</v>
+        <v>0.3039405209356261</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09402700856120083</v>
+        <v>0.08075187149898154</v>
       </c>
       <c r="R5" s="5">
         <v>7</v>
@@ -1857,16 +1857,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3846529860302823</v>
+        <v>0.4223471377978569</v>
       </c>
       <c r="O3" s="5">
         <v>8</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6727390802666744</v>
+        <v>0.66769642639724</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.08106772427245446</v>
+        <v>0.06816164276367687</v>
       </c>
       <c r="R3" s="5">
         <v>8</v>
@@ -1916,16 +1916,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.2268950187045359</v>
+        <v>0.1683629133312365</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.3084721794938504</v>
+        <v>0.3089078971814908</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1491070327893474</v>
+        <v>0.1367292682552059</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4109933237658581</v>
+        <v>0.3868196170666636</v>
       </c>
       <c r="O5" s="5">
         <v>8</v>
       </c>
       <c r="P5" s="4">
-        <v>0.334404263451023</v>
+        <v>0.332808296078722</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09056256693846443</v>
+        <v>0.08494740662107603</v>
       </c>
       <c r="R5" s="5">
         <v>8</v>
@@ -2157,16 +2157,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0991003958475587</v>
+        <v>-0.1449239590655154</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1145948400549929</v>
+        <v>0.111399336922903</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1188336581411153</v>
+        <v>0.1115532328131882</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2216,16 +2216,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.06547280116934751</v>
+        <v>-0.08319110235207994</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.08920638289229725</v>
+        <v>0.08784343664747168</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08920638289229725</v>
+        <v>0.08784343664747168</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -2275,16 +2275,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03724708171536761</v>
+        <v>-0.0662559248013963</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06895591657590654</v>
+        <v>0.06223304086116681</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06895591657590654</v>
+        <v>0.06223304086116681</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -2457,13 +2457,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.02705539469075783</v>
+        <v>0.04460766585935971</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1403859095640449</v>
+        <v>0.1390357348587678</v>
       </c>
       <c r="Q3" s="4">
         <v>0.1293271273469969</v>
@@ -2516,16 +2516,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07901389253342188</v>
+        <v>0.02929587729121863</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.187153422090143</v>
+        <v>0.1815400481219871</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1394472046031262</v>
+        <v>0.1371216199687439</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -2575,16 +2575,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.3018488195308369</v>
+        <v>0.2397214604943656</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1576714098888291</v>
+        <v>0.1485954612650263</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.139665848194451</v>
+        <v>0.1246562905989587</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -2757,16 +2757,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.03136332020304641</v>
+        <v>-0.02137470869016056</v>
       </c>
       <c r="O3" s="5">
         <v>12</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1460705544320837</v>
+        <v>0.1369928518870154</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1272410524565891</v>
+        <v>0.1130120389583311</v>
       </c>
       <c r="R3" s="5">
         <v>12</v>
@@ -2816,16 +2816,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.01423484345482014</v>
+        <v>-0.08626013260195009</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1842611179071499</v>
+        <v>0.1708111738732065</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1479089757899254</v>
+        <v>0.1273360956575592</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -2875,16 +2875,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.03754846793925518</v>
+        <v>-0.1013837601593366</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2154358813596826</v>
+        <v>0.2027786788762197</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1883819481163269</v>
+        <v>0.1693503710742353</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -3057,16 +3057,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1582036947861918</v>
+        <v>0.1072132073132366</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1605708289330545</v>
+        <v>0.1488709657421798</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1605708289330545</v>
+        <v>0.1488709657421798</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3116,16 +3116,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1259552244225119</v>
+        <v>-0.1817613697662637</v>
       </c>
       <c r="O4" s="5">
         <v>10</v>
       </c>
       <c r="P4" s="4">
-        <v>0.144598092171868</v>
+        <v>0.1417081729146551</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1164150217249926</v>
+        <v>0.1070775121562406</v>
       </c>
       <c r="R4" s="5">
         <v>10</v>
@@ -3175,16 +3175,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.07727036190613035</v>
+        <v>-0.1325910072186502</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1260117646334213</v>
+        <v>0.1208489370853359</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1450384903409217</v>
+        <v>0.1288786677272717</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -3357,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.3383647215941807</v>
+        <v>0.3311795809407236</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09694863112086546</v>
+        <v>0.09639592799367645</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09694863112086546</v>
+        <v>0.09639592799367645</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3416,16 +3416,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.212173053375108</v>
+        <v>0.2094069548450648</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.04120002294756089</v>
+        <v>0.04048712291311892</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04120002294756089</v>
+        <v>0.04048712291311892</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3475,16 +3475,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2753748556911857</v>
+        <v>0.2712971587322386</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.05853481711082912</v>
+        <v>0.05822114811398704</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.05853481711082912</v>
+        <v>0.05822114811398704</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -3657,16 +3657,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2271785884062033</v>
+        <v>-0.21219500396111</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0457271870504475</v>
+        <v>0.04457460363159417</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0457271870504475</v>
+        <v>0.04457460363159417</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -3716,16 +3716,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.2937280901527891</v>
+        <v>-0.2963472853502935</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06020185808886454</v>
+        <v>0.05961201883354569</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06020185808886454</v>
+        <v>0.05961201883354569</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.4541047872519931</v>
+        <v>-0.4651111222922779</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.06086316700552007</v>
+        <v>0.06001652584857508</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.06086316700552007</v>
+        <v>0.06001652584857508</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -3957,16 +3957,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4480221231103311</v>
+        <v>0.4410178311504183</v>
       </c>
       <c r="O3" s="5">
         <v>9</v>
       </c>
       <c r="P3" s="4">
-        <v>0.3172069721846377</v>
+        <v>0.3173040861654775</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07822524404388347</v>
+        <v>0.07680901046956023</v>
       </c>
       <c r="R3" s="5">
         <v>9</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.4585154380045842</v>
+        <v>0.4553700273693799</v>
       </c>
       <c r="O4" s="5">
         <v>9</v>
       </c>
       <c r="P4" s="4">
-        <v>0.4980407677106606</v>
+        <v>0.4976415177776013</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.04278618283005669</v>
+        <v>0.0422094884823044</v>
       </c>
       <c r="R4" s="5">
         <v>9</v>
@@ -4075,16 +4075,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.5195863095416726</v>
+        <v>0.5168668769620623</v>
       </c>
       <c r="O5" s="5">
         <v>9</v>
       </c>
       <c r="P5" s="4">
-        <v>0.2734623282124252</v>
+        <v>0.2740898895769507</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.04918116609057677</v>
+        <v>0.04887900691506451</v>
       </c>
       <c r="R5" s="5">
         <v>9</v>
@@ -4257,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2041711382107484</v>
+        <v>-0.2194814004214436</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.06564330956672569</v>
+        <v>0.06446559708897991</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06564330956672569</v>
+        <v>0.06446559708897991</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -4316,16 +4316,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>-0.1828719131732498</v>
+        <v>-0.2144149511389024</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09976196138479446</v>
+        <v>0.09380897362462985</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.08018915954735462</v>
+        <v>0.07636867597098067</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -4375,16 +4375,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>-0.2178745687949313</v>
+        <v>-0.2845077488347236</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.1143448592261962</v>
+        <v>0.1018442138304118</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1226659938528189</v>
+        <v>0.1059860702885237</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -4521,13 +4521,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1281031997854639</v>
+        <v>0.1167356530428633</v>
       </c>
       <c r="I3" s="4">
-        <v>0.1295221022865</v>
+        <v>0.1193512365028735</v>
       </c>
       <c r="J3" s="4">
-        <v>0.1568394511201326</v>
+        <v>0.1472558394137491</v>
       </c>
       <c r="K3" s="4">
         <v>85.85382871097174</v>
@@ -4571,13 +4571,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1040909104757614</v>
+        <v>0.09337290209260028</v>
       </c>
       <c r="I4" s="4">
-        <v>0.1040909104757614</v>
+        <v>0.09337290209260028</v>
       </c>
       <c r="J4" s="4">
-        <v>0.184793281014352</v>
+        <v>0.1689358135729676</v>
       </c>
       <c r="K4" s="4">
         <v>83.67695796267225</v>
@@ -4621,13 +4621,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.08623896169522165</v>
+        <v>0.08616400956325612</v>
       </c>
       <c r="I5" s="4">
-        <v>0.08503854888648345</v>
+        <v>0.08335042484158982</v>
       </c>
       <c r="J5" s="4">
-        <v>0.1128496285675564</v>
+        <v>0.1107561267979658</v>
       </c>
       <c r="K5" s="4">
         <v>86.43467643467652</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.1382730864226216</v>
+        <v>0.1399458863221096</v>
       </c>
       <c r="I6" s="4">
-        <v>0.08808425465178117</v>
+        <v>0.08806880987722414</v>
       </c>
       <c r="J6" s="4">
-        <v>0.1953070774963913</v>
+        <v>0.1968306250882618</v>
       </c>
       <c r="K6" s="4">
         <v>76.93615907901597</v>
@@ -4721,13 +4721,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.08599551651040786</v>
+        <v>0.08098809154646912</v>
       </c>
       <c r="I7" s="4">
-        <v>0.07926236149404446</v>
+        <v>0.07468563659333495</v>
       </c>
       <c r="J7" s="4">
-        <v>0.07360441025201638</v>
+        <v>0.06899209796438226</v>
       </c>
       <c r="K7" s="4">
         <v>90.38548752834464</v>
@@ -4771,13 +4771,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.234860334135978</v>
+        <v>0.2222970136082602</v>
       </c>
       <c r="I8" s="4">
-        <v>0.1630470915425276</v>
+        <v>0.1456541663951372</v>
       </c>
       <c r="J8" s="4">
-        <v>0.2042146514296665</v>
+        <v>0.1963469466286457</v>
       </c>
       <c r="K8" s="4">
         <v>84.25954997383553</v>
@@ -4821,13 +4821,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.4385385077371826</v>
+        <v>0.436470873219151</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1086002249916591</v>
+        <v>0.09821743237499504</v>
       </c>
       <c r="J9" s="4">
-        <v>0.4134500546662846</v>
+        <v>0.4151701215134187</v>
       </c>
       <c r="K9" s="4">
         <v>57.95133437990611</v>
@@ -4871,13 +4871,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.09091904650773222</v>
+        <v>0.08715860481051384</v>
       </c>
       <c r="I10" s="4">
-        <v>0.09163457344157981</v>
+        <v>0.08656928950975155</v>
       </c>
       <c r="J10" s="4">
-        <v>0.1244874417201523</v>
+        <v>0.126992368049254</v>
       </c>
       <c r="K10" s="4">
         <v>87.76033490319197</v>
@@ -4921,13 +4921,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1617369138476723</v>
+        <v>0.1563904147485937</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1359525809567246</v>
+        <v>0.1299710945599678</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1594332780295425</v>
+        <v>0.1556377643991625</v>
       </c>
       <c r="K11" s="4">
         <v>84.12175126460838</v>
@@ -4971,13 +4971,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.1819225178996388</v>
+        <v>0.1701942348788139</v>
       </c>
       <c r="I12" s="4">
-        <v>0.1545106587876138</v>
+        <v>0.1365661685633752</v>
       </c>
       <c r="J12" s="4">
-        <v>0.1671786151552478</v>
+        <v>0.1600836348177119</v>
       </c>
       <c r="K12" s="4">
         <v>89.40258154543861</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.1437268952461146</v>
+        <v>0.1371426919140569</v>
       </c>
       <c r="I13" s="4">
-        <v>0.1425586584449933</v>
+        <v>0.1301106770944333</v>
       </c>
       <c r="J13" s="4">
-        <v>0.1592011322510214</v>
+        <v>0.153274013706927</v>
       </c>
       <c r="K13" s="4">
         <v>84.01098901098891</v>
@@ -5071,13 +5071,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.06556115705975184</v>
+        <v>0.06503473300692747</v>
       </c>
       <c r="I14" s="4">
-        <v>0.06556115705975184</v>
+        <v>0.06503473300692747</v>
       </c>
       <c r="J14" s="4">
-        <v>0.05126534200207447</v>
+        <v>0.05146254318316296</v>
       </c>
       <c r="K14" s="4">
         <v>81.90912262340832</v>
@@ -5121,13 +5121,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.05559740404827736</v>
+        <v>0.05473438277123831</v>
       </c>
       <c r="I15" s="4">
-        <v>0.05559740404827736</v>
+        <v>0.05473438277123831</v>
       </c>
       <c r="J15" s="4">
-        <v>0.04719270808241108</v>
+        <v>0.04848667966368508</v>
       </c>
       <c r="K15" s="4">
         <v>95.49973835688124</v>
@@ -5171,13 +5171,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="4">
-        <v>0.3629033560359078</v>
+        <v>0.3630118311733432</v>
       </c>
       <c r="I16" s="4">
-        <v>0.05673086432150564</v>
+        <v>0.05596583528897638</v>
       </c>
       <c r="J16" s="4">
-        <v>0.1057921688339227</v>
+        <v>0.1061221466589156</v>
       </c>
       <c r="K16" s="4">
         <v>62.31728588871481</v>
@@ -5221,13 +5221,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="4">
-        <v>0.09325004339257212</v>
+        <v>0.08670626151467385</v>
       </c>
       <c r="I17" s="4">
-        <v>0.0888547260856626</v>
+        <v>0.0817921545208322</v>
       </c>
       <c r="J17" s="4">
-        <v>0.08932307863232167</v>
+        <v>0.08281360533932879</v>
       </c>
       <c r="K17" s="4">
         <v>93.84528170242461</v>
@@ -6924,16 +6924,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.2736053295893769</v>
+        <v>0.2665651978405776</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1061071413063905</v>
+        <v>0.105565592710329</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1061071413063905</v>
+        <v>0.105565592710329</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -6983,16 +6983,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.07117880260077833</v>
+        <v>-0.02094664817445846</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1451105569397182</v>
+        <v>0.1332327498737916</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.1451105569397182</v>
+        <v>0.1332327498737916</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -7042,16 +7042,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.4233615344512884</v>
+        <v>0.3665201112676755</v>
       </c>
       <c r="O5" s="5">
         <v>12</v>
       </c>
       <c r="P5" s="4">
-        <v>0.133091901110283</v>
+        <v>0.1114086165444694</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.1380008174739658</v>
+        <v>0.1192473777929687</v>
       </c>
       <c r="R5" s="5">
         <v>12</v>
@@ -7224,16 +7224,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.005274572154825399</v>
+        <v>0.01235359578123507</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.0588052271208123</v>
+        <v>0.05731475371957318</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.0588052271208123</v>
+        <v>0.05731475371957318</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01374862696624746</v>
+        <v>0.01544575765620948</v>
       </c>
       <c r="O4" s="5">
         <v>13</v>
       </c>
       <c r="P4" s="4">
-        <v>0.06412052342709383</v>
+        <v>0.06398997491248136</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06412052342709383</v>
+        <v>0.06398997491248136</v>
       </c>
       <c r="R4" s="5">
         <v>13</v>
@@ -7340,16 +7340,16 @@
         <v>13</v>
       </c>
       <c r="N5" s="4">
-        <v>3.763579802575866</v>
+        <v>3.84825800291992</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.189346980879378</v>
+        <v>0.1588139776457463</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.189346980879378</v>
+        <v>0.1588139776457463</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
@@ -7522,16 +7522,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.05910295602238263</v>
+        <v>0.0648700238617721</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09399194032746047</v>
+        <v>0.09354831972443051</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09399194032746047</v>
+        <v>0.09354831972443051</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -7581,16 +7581,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.01262863094403125</v>
+        <v>-0.006288707366678636</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.07370064606032309</v>
+        <v>0.07242202587673319</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.06508462086531747</v>
+        <v>0.06212300414053592</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -7640,16 +7640,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.0456741326339108</v>
+        <v>0.0651401297133134</v>
       </c>
       <c r="O5" s="5">
         <v>11</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09102429869788138</v>
+        <v>0.09252168308860466</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09622518957023715</v>
+        <v>0.09445555347210964</v>
       </c>
       <c r="R5" s="5">
         <v>11</v>
@@ -7822,13 +7822,13 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.170237371803961</v>
+        <v>0.1663182294836645</v>
       </c>
       <c r="O3" s="5">
         <v>10</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1328572662944571</v>
+        <v>0.133761683752987</v>
       </c>
       <c r="Q3" s="4">
         <v>0.09500752974217334</v>
@@ -7881,13 +7881,13 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.0188044097417901</v>
+        <v>0.02841557496640235</v>
       </c>
       <c r="O4" s="5">
         <v>8</v>
       </c>
       <c r="P4" s="4">
-        <v>0.1735097857083758</v>
+        <v>0.1727704653064826</v>
       </c>
       <c r="Q4" s="4">
         <v>0.0991196888183481</v>
@@ -7940,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.2107319703953806</v>
+        <v>0.1895568410515978</v>
       </c>
       <c r="O5" s="5">
         <v>10</v>
       </c>
       <c r="P5" s="4">
-        <v>0.108452207265032</v>
+        <v>0.113305509906859</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.07233263222813549</v>
+        <v>0.07228938685937578</v>
       </c>
       <c r="R5" s="5">
         <v>10</v>
@@ -8122,16 +8122,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>0.1433644857431292</v>
+        <v>0.1353496166235004</v>
       </c>
       <c r="O3" s="5">
         <v>13</v>
       </c>
       <c r="P3" s="4">
-        <v>0.07196181708070594</v>
+        <v>0.07134528868688833</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.07196181708070594</v>
+        <v>0.07134528868688833</v>
       </c>
       <c r="R3" s="5">
         <v>13</v>
@@ -8181,16 +8181,16 @@
         <v>0</v>
       </c>
       <c r="N4" s="4">
-        <v>0.1227882179037205</v>
+        <v>0.1014141905370707</v>
       </c>
       <c r="O4" s="5">
         <v>12</v>
       </c>
       <c r="P4" s="4">
-        <v>0.09350277899317587</v>
+        <v>0.08670035880408242</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.07280672664825576</v>
+        <v>0.06721860705729199</v>
       </c>
       <c r="R4" s="5">
         <v>12</v>
@@ -8240,16 +8240,16 @@
         <v>0</v>
       </c>
       <c r="N5" s="4">
-        <v>0.1661359468500642</v>
+        <v>0.1297500193694532</v>
       </c>
       <c r="O5" s="5">
         <v>13</v>
       </c>
       <c r="P5" s="4">
-        <v>0.09252195345734181</v>
+        <v>0.08491862714843662</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.09252195345734181</v>
+        <v>0.08491862714843662</v>
       </c>
       <c r="R5" s="5">
         <v>13</v>
